--- a/projets/nba-mi-distance/excel/nba-mi-distance-exercice.xlsx
+++ b/projets/nba-mi-distance/excel/nba-mi-distance-exercice.xlsx
@@ -16,6 +16,10 @@
     <sheet name="Terrain 2004" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Terrain 2025" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">'Terrain 2004'!$A$1:$Z$20</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Terrain 2025'!$A$1:$Z$20</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -28,7 +32,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="79">
   <si>
-    <t xml:space="preserve">Le tir que la NBA a arrêté de financer — EXERCICE</t>
+    <t xml:space="preserve">Le tir que la NBA a arrêté de financer · EXERCICE</t>
   </si>
   <si>
     <t xml:space="preserve">Exercice : les cellules jaunes sont à remplir, les graphiques à construire. Suivez TUTO.md (ou la page Tuto du site), étape par étape.</t>
@@ -256,7 +260,7 @@
     <t xml:space="preserve">Carte des tirs 2003-04 : part des tirs (‰) par case de 2 × 2 pieds</t>
   </si>
   <si>
-    <t xml:space="preserve">Ligne du haut = au niveau du panier. Plus c'est rouge, plus on tire de là.</t>
+    <t xml:space="preserve">Ligne du haut = au niveau du panier. Plus c'est rouge, plus on tire de là. Même échelle de couleurs pour les deux saisons.</t>
   </si>
   <si>
     <t xml:space="preserve">À faire : la mise en forme conditionnelle (étape 5).</t>
@@ -2356,7 +2360,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:Z20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -3610,8 +3614,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3622,7 +3626,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:Z20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -4860,8 +4864,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
